--- a/KatalonData/EmailTextToPay/BillFileLookUp_Upgrade.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Upgrade.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE0C132-F71E-462D-B9A9-D5C229D3B52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B3718C-9332-4570-842C-BE5A9E7110E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="BFLU" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="131">
   <si>
     <t>Result</t>
   </si>
@@ -269,9 +269,6 @@
     <t>Patel Companys</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
     <t>Payment app+ 1st + 2nd +3rd lookup</t>
   </si>
   <si>
@@ -287,242 +284,163 @@
     <t>45332116803cA</t>
   </si>
   <si>
-    <t>Mon Jul 13 14:09:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:13:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:18:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:18:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:19:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:20:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:21:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:22:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:25:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:26:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:27:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:15:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:16:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:17:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:17:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:18:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:19:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:20:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:21:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:22:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:23:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:23:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:24:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:25:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:43:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:44:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:45:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:51:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:52:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:53:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:53:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:54:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:55:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:55:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:56:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:57:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:58:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:58:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:59:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:00:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:01:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:02:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:03:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:04:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:05:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:05:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:06:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:07:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 16:08:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:52:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 21:52:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:05:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:05:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:06:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:07:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:08:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:08:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:09:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:10:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:10:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:11:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:12:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:12:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:13:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:14:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:14:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:15:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:16:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:17:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:17:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:18:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:19:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:19:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:20:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:21:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:21:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 17 23:22:23 IST 2026</t>
+    <t>Thu Oct 15 08:20:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:22:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:22:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:23:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:24:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:24:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:25:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:26:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:26:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:27:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:28:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:28:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:29:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:30:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:30:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:31:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:32:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:32:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:33:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:34:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:35:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:35:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 08:36:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 16:55:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 16:56:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 16:59:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 16:59:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:00:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:03:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:04:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:05:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:06:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:07:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:07:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:08:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:09:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:10:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:11:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:12:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:13:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 15 17:13:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:15:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:16:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:17:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:18:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:19:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:20:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:20:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 16 13:21:38 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -548,18 +466,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -589,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -614,9 +526,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -955,18 +864,18 @@
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="3" width="17.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="35.453125" collapsed="true"/>
-    <col min="4" max="4" style="3" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="24.90625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="3" width="11.26953125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="25.6328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="7" width="13.54296875" collapsed="true"/>
-    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="17" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="3" collapsed="1"/>
+    <col min="5" max="5" width="24.90625" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="11.26953125" style="3" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.7265625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="25.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.54296875" style="7" customWidth="1" collapsed="1"/>
+    <col min="12" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1009,7 +918,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -1025,11 +934,11 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -1045,11 +954,11 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -1065,11 +974,11 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -1089,7 +998,7 @@
         <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>55</v>
@@ -1109,7 +1018,7 @@
         <v>70</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1129,7 +1038,7 @@
         <v>70</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1149,7 +1058,7 @@
         <v>70</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
@@ -1184,7 +1093,7 @@
         <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
@@ -1203,11 +1112,11 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
@@ -1226,11 +1135,11 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>38</v>
@@ -1253,7 +1162,7 @@
         <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
@@ -1276,7 +1185,7 @@
         <v>70</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
@@ -1299,7 +1208,7 @@
         <v>70</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1322,7 +1231,7 @@
         <v>70</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1345,7 +1254,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>56</v>
@@ -1368,7 +1277,7 @@
         <v>70</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
@@ -1391,7 +1300,7 @@
         <v>70</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
@@ -1414,7 +1323,7 @@
         <v>70</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>57</v>
@@ -1437,7 +1346,7 @@
         <v>70</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>54</v>
@@ -1463,7 +1372,7 @@
         <v>70</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1486,7 +1395,7 @@
         <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>153</v>
+        <v>111</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1509,7 +1418,7 @@
         <v>70</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>58</v>
@@ -1532,7 +1441,7 @@
         <v>70</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>113</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1555,7 +1464,7 @@
         <v>70</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -1578,7 +1487,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>59</v>
@@ -1608,18 +1517,18 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="3" width="11.08984375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="35.453125" collapsed="true"/>
-    <col min="4" max="4" style="3" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="24.90625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="14.453125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="25.6328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="7" width="13.54296875" collapsed="true"/>
-    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="11.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="3" collapsed="1"/>
+    <col min="5" max="5" width="24.90625" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.453125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.7265625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="25.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.54296875" style="7" customWidth="1" collapsed="1"/>
+    <col min="12" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1662,10 +1571,10 @@
         <v>70</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
@@ -1688,10 +1597,10 @@
         <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
@@ -1700,7 +1609,7 @@
         <v>71</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
@@ -1708,10 +1617,10 @@
         <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
@@ -1720,7 +1629,7 @@
         <v>71</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1734,19 +1643,19 @@
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="5" width="10.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="30.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="3" width="7.81640625" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="25.1796875" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="10.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.81640625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="15.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.81640625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="3" width="13.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="5" width="45.1796875" collapsed="true"/>
-    <col min="13" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="10.90625" style="5" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="30.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="7.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="25.1796875" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="10.81640625" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.54296875" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13" style="3" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="45.1796875" style="5" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
@@ -1792,7 +1701,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -1815,7 +1724,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -1838,7 +1747,7 @@
         <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -1861,7 +1770,7 @@
         <v>70</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -1884,7 +1793,7 @@
         <v>70</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>39</v>
@@ -1907,7 +1816,7 @@
         <v>70</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>40</v>
@@ -1930,7 +1839,7 @@
         <v>70</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>41</v>
@@ -1956,7 +1865,7 @@
         <v>70</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>42</v>
@@ -1982,7 +1891,7 @@
         <v>70</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
@@ -2008,7 +1917,7 @@
         <v>70</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>43</v>
@@ -2034,7 +1943,7 @@
         <v>70</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>49</v>
@@ -2060,7 +1969,7 @@
         <v>70</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>50</v>
@@ -2086,7 +1995,7 @@
         <v>70</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>51</v>
@@ -2112,7 +2021,7 @@
         <v>70</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>45</v>
@@ -2138,7 +2047,7 @@
         <v>70</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>46</v>
@@ -2164,7 +2073,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>47</v>
@@ -2190,7 +2099,7 @@
         <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>48</v>
@@ -2216,7 +2125,7 @@
         <v>70</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>64</v>
@@ -2239,7 +2148,7 @@
         <v>70</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>66</v>
@@ -2265,7 +2174,7 @@
         <v>70</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>67</v>
@@ -2291,7 +2200,7 @@
         <v>70</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>68</v>
@@ -2317,7 +2226,7 @@
         <v>70</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>69</v>
